--- a/Sedes_a_priorizar_COTAINDOC.xlsx
+++ b/Sedes_a_priorizar_COTAINDOC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,11 +478,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>219743000511</v>
+        <v>219743000180</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C.E. NAZARETH - SEDE PRINCIPAL</t>
+          <t>CENTRO DOCENTE RURAL MIXTO MIRAFLORES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,7 +492,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PITAYO</t>
+          <t>AMPIUILE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49.04590681034483</v>
+        <v>48.73261293103449</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>219824000427</v>
+        <v>219743000511</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CENTRO DOCENTE RURAL MIXTO EL BAHO</t>
+          <t>C.E. NAZARETH - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -520,25 +520,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>POLINDARA</t>
+          <t>PITAYO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TOTORO</t>
+          <t>SILVIA</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50.80761189655173</v>
+        <v>49.04590681034483</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>219824000095</v>
+        <v>219824000427</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ESCUELA SAN ANTONIO</t>
+          <t>CENTRO DOCENTE RURAL MIXTO EL BAHO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PANIQUITA</t>
+          <t>POLINDARA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50.90423405172414</v>
+        <v>50.80761189655173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>419743001096</v>
+        <v>219824000095</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CENTRO DOCENTE RURAL MIXTO GOLONDRINAS</t>
+          <t>ESCUELA SAN ANTONIO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,43 +576,71 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>QUICHAYA</t>
+          <t>PANIQUITA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SILVIA</t>
+          <t>TOTORO</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>51.78705086206897</v>
+        <v>50.90423405172414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>419743001096</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CENTRO DOCENTE RURAL MIXTO GOLONDRINAS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ZONA ORIENTE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>QUICHAYA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SILVIA</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>51.78705086206897</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>219824800017</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>LA PRIMAVERA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>ZONA ORIENTE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>PANIQUITA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>TOTORO</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>53.46349077586207</v>
       </c>
     </row>
